--- a/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2022_coquimbo_sexo.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2022_coquimbo_sexo.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 15:06</t>
+    <t xml:space="preserve">2026-10-05 06:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -478,7 +478,7 @@
         <v>2.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
